--- a/grades.xlsx
+++ b/grades.xlsx
@@ -280,7 +280,6 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1"/>
       <c r="C6" s="0">
         <f>AVERAGE(C2:C5)</f>
       </c>
